--- a/crassets.xlsx
+++ b/crassets.xlsx
@@ -62,9 +62,6 @@
     <t>Oracle</t>
   </si>
   <si>
-    <t>AAVE</t>
-  </si>
-  <si>
     <t>KI</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <t>AIOZ</t>
+  </si>
+  <si>
+    <t>CRO</t>
   </si>
 </sst>
 </file>
@@ -465,12 +465,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -498,7 +498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -512,7 +512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -526,312 +526,312 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>12.08</v>
+        <v>369</v>
       </c>
       <c r="C5">
-        <v>66.3</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>4075</v>
+      </c>
+      <c r="C6">
+        <v>1.4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>6367</v>
+      </c>
+      <c r="C7">
+        <v>0.25290000000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>239926</v>
+      </c>
+      <c r="C8">
+        <v>1.7729999999999999E-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>369</v>
-      </c>
-      <c r="C6">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>4075</v>
-      </c>
-      <c r="C7">
-        <v>1.4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>6367</v>
-      </c>
-      <c r="C8">
-        <v>0.25290000000000001</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B9">
+        <v>56240</v>
+      </c>
+      <c r="C9">
+        <v>0.08</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>239926</v>
-      </c>
-      <c r="C9">
-        <v>1.7729999999999999E-2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>56240</v>
+        <v>228</v>
       </c>
       <c r="C10">
-        <v>0.08</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>228</v>
+        <v>7677</v>
       </c>
       <c r="C11">
-        <v>0.49399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>7677</v>
+        <v>2341.8000000000002</v>
       </c>
       <c r="C12">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>2341.8000000000002</v>
+        <v>476.87</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>476.87</v>
+        <v>269.7</v>
       </c>
       <c r="C14">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>269.7</v>
+        <v>30.67</v>
       </c>
       <c r="C15">
-        <v>9.4</v>
+        <v>37.6</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>30.67</v>
+        <v>14531</v>
       </c>
       <c r="C16">
-        <v>37.6</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>14531</v>
+        <v>3161</v>
       </c>
       <c r="C17">
-        <v>7.0000000000000007E-2</v>
+        <v>1.5</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
       <c r="B18">
-        <v>3161</v>
+        <v>5903</v>
       </c>
       <c r="C18">
-        <v>1.5</v>
+        <v>1.0609999999999999</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>5903</v>
+        <v>300</v>
       </c>
       <c r="C19">
-        <v>1.0609999999999999</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>300</v>
+        <v>3153</v>
       </c>
       <c r="C20">
-        <v>4.3499999999999996</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
-        <v>3153</v>
+        <v>98839</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22">
-        <v>98839</v>
+        <v>775</v>
       </c>
       <c r="C22">
-        <v>8.0000000000000002E-3</v>
+        <v>1.4</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23">
-        <v>775</v>
+        <v>4295</v>
       </c>
       <c r="C23">
-        <v>1.4</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24">
-        <v>3073</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C24">
-        <v>1.04</v>
+        <v>45000</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25">
-        <v>6.0000000000000001E-3</v>
+        <v>7693</v>
       </c>
       <c r="C25">
-        <v>45000</v>
+        <v>0.46</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>38</v>
       </c>
       <c r="B26">
-        <v>4621</v>
+        <v>4162</v>
       </c>
       <c r="C26">
-        <v>0.5</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
